--- a/data/trans_orig/IP3108-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3108-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113568</t>
+          <t>113303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123399</t>
+          <t>123250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123780</t>
+          <t>123728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134672</t>
+          <t>134346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>241597</t>
+          <t>241381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255932</t>
+          <t>255697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149793</t>
+          <t>150438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163291</t>
+          <t>163197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176483</t>
+          <t>176672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189394</t>
+          <t>189407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331909</t>
+          <t>331932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349918</t>
+          <t>350167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108940</t>
+          <t>108851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>119054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119525</t>
+          <t>119400</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128986</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231858</t>
+          <t>231747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245698</t>
+          <t>245582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172240</t>
+          <t>173079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186143</t>
+          <t>186542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>171068</t>
+          <t>171063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183489</t>
+          <t>183251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>347989</t>
+          <t>348887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366857</t>
+          <t>366675</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56926</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>559438</t>
+          <t>559304</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>582590</t>
+          <t>583117</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>603004</t>
+          <t>605200</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>626989</t>
+          <t>627636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1171440</t>
+          <t>1170816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1204376</t>
+          <t>1205037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114559</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125067</t>
+          <t>125145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128592</t>
+          <t>129642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137318</t>
+          <t>136943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247354</t>
+          <t>247656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260322</t>
+          <t>260509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158205</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172698</t>
+          <t>172850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177558</t>
+          <t>177362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190560</t>
+          <t>190919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340908</t>
+          <t>341673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360610</t>
+          <t>360877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>125477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>134386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136361</t>
+          <t>135929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>145046</t>
+          <t>144943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264538</t>
+          <t>265448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>277393</t>
+          <t>277660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161946</t>
+          <t>161970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>176050</t>
+          <t>176099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>170927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183294</t>
+          <t>183440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>337902</t>
+          <t>338519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>356621</t>
+          <t>356482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>574626</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>599087</t>
+          <t>598841</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>626745</t>
+          <t>625489</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>648759</t>
+          <t>648376</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1209548</t>
+          <t>1209752</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1241066</t>
+          <t>1241410</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104652</t>
+          <t>104182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114781</t>
+          <t>114295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>118447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129240</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228073</t>
+          <t>226726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>241923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21964</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167158</t>
+          <t>167689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178771</t>
+          <t>179679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186082</t>
+          <t>185936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197189</t>
+          <t>197137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357440</t>
+          <t>357080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374851</t>
+          <t>373830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119790</t>
+          <t>119373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130886</t>
+          <t>130569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126362</t>
+          <t>126504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140214</t>
+          <t>140697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249973</t>
+          <t>249685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268241</t>
+          <t>268213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167211</t>
+          <t>166881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180540</t>
+          <t>180092</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169359</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>340859</t>
+          <t>342282</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357722</t>
+          <t>357853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>39584</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>571879</t>
+          <t>572041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>594843</t>
+          <t>595494</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>615182</t>
+          <t>614476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>638261</t>
+          <t>638464</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1196092</t>
+          <t>1194613</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1228129</t>
+          <t>1227350</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
